--- a/next-app/Excel File/NEW List Pengajuan Verifikasi MCU KPC.xlsx
+++ b/next-app/Excel File/NEW List Pengajuan Verifikasi MCU KPC.xlsx
@@ -1351,7 +1351,7 @@
         <v>Estimated Average Glucose</v>
       </c>
       <c r="C10">
-        <v>108.3</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="11">
